--- a/new_model/model_Fe_Si_B_260311/scmace_0.0001_60_10_rnd_e/test_res/model_rnd_e_scmace_lr0.0001_60_10_test.xlsx
+++ b/new_model/model_Fe_Si_B_260311/scmace_0.0001_60_10_rnd_e/test_res/model_rnd_e_scmace_lr0.0001_60_10_test.xlsx
@@ -27018,10 +27018,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.571505047541216</v>
+        <v>571.5050475412161</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3121599616396396</v>
+        <v>312.1599616396396</v>
       </c>
       <c r="E4" t="n">
         <v>0.9582093193606304</v>
@@ -27037,13 +27037,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.421373144862466</v>
+        <v>421.3731448624661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.311004647757855</v>
+        <v>311.004647757855</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9770578681089137</v>
+        <v>0.9770578681089138</v>
       </c>
     </row>
   </sheetData>
